--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -1938,13 +1938,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1960,12 +1962,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Maximo</t>
+          <t>Maximo Atual</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Media (%)</t>
+          <t>Pontos Pendentes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Media Atual (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Projecao Final (%)</t>
         </is>
       </c>
     </row>
@@ -1982,70 +1994,56 @@
         <v>20</v>
       </c>
       <c r="D2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2" t="n">
         <v>95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Experiencia Criativa</t>
+          <t>Raciocinio Algoritmico</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52.8</v>
+        <v>18.11</v>
       </c>
       <c r="C3" t="n">
-        <v>110</v>
+        <v>32.5</v>
       </c>
       <c r="D3" t="n">
-        <v>48</v>
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="F3" t="n">
+        <v>55.72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Filosofia</t>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46</v>
+        <v>61.4</v>
       </c>
       <c r="C4" t="n">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="D4" t="n">
-        <v>65.70999999999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Raciocinio Algoritmico</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>18.11</v>
-      </c>
-      <c r="C5" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>55.72</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Fundamentos Sistemas Ciberfisicos</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>123</v>
-      </c>
-      <c r="D6" t="n">
+        <v>467</v>
+      </c>
+      <c r="E4" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="F4" t="n">
         <v>49.92</v>
       </c>
     </row>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -472,12 +472,18 @@
           <t>Atividade Aula 03</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atencao</t>
         </is>
       </c>
     </row>
@@ -487,12 +493,18 @@
           <t>Envio TDE</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
         <v>10</v>
       </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atencao</t>
         </is>
       </c>
     </row>
@@ -559,12 +571,39 @@
           <t>Tarefa da aula 08 (21/05)</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2º AVALIAÇÃO SOMATIVA</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Atencao</t>
         </is>
       </c>
     </row>
@@ -1988,19 +2027,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>41.67</v>
       </c>
       <c r="F2" t="n">
-        <v>95</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="3">
@@ -2058,7 +2097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2091,7 +2130,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Atividade Aula 03</t>
+          <t>Atividade Extensionista</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2101,12 +2140,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aspectos Legais</t>
+          <t>Raciocinio Algoritmico</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Envio TDE</t>
+          <t>Prova 1</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2116,46 +2155,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aspectos Legais</t>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Atividade Extensionista</t>
+          <t>Conversão de Bases - Exercícios Adionais</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aspectos Legais</t>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tarefa da aula 08 (21/05)</t>
+          <t>Limites números binários - Exercícios Adicionais</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Raciocinio Algoritmico</t>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prova 1</t>
+          <t>Números Negativos - Exercícios Adicionais</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -2166,11 +2205,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Conversão de Bases - Exercícios Adionais</t>
+          <t>Operações em Outras Bases - Exercícios Adicionais</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -2181,11 +2220,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Limites números binários - Exercícios Adicionais</t>
+          <t>Bitwise - Exercícios Adicionais</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -2196,11 +2235,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Números Negativos - Exercícios Adicionais</t>
+          <t>CRE1.Cumulative Reinforcement Exercise 1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -2211,11 +2250,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Operações em Outras Bases - Exercícios Adicionais</t>
+          <t>CRE2.Cumulative Reinforcement Exercise 2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -2226,11 +2265,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bitwise - Exercícios Adicionais</t>
+          <t>CRE3.Cumulative Reinforcement Exercise 3</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -2241,11 +2280,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CRE1.Cumulative Reinforcement Exercise 1</t>
+          <t>CRE8.Cumulative Reinforcement Exercise 8</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -2256,11 +2295,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CRE2.Cumulative Reinforcement Exercise 2</t>
+          <t>CRE9.Cumulative Reinforcement Exercise 9</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -2271,11 +2310,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CRE3.Cumulative Reinforcement Exercise 3</t>
+          <t>CRE10.Cumulative Reinforcement Exercise 10</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -2286,11 +2325,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CRE8.Cumulative Reinforcement Exercise 8</t>
+          <t>CRE11.Cumulative Reinforcement Exercise 11</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -2301,11 +2340,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CRE9.Cumulative Reinforcement Exercise 9</t>
+          <t>CRE12.Cumulative Reinforcement Exercise 12 - Sistemas Operacionais</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17">
@@ -2316,11 +2355,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CRE10.Cumulative Reinforcement Exercise 10</t>
+          <t>CRE13.Cumulative Reinforcement Exercise 13 - Comunicação de Dados</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
@@ -2331,11 +2370,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CRE11.Cumulative Reinforcement Exercise 11</t>
+          <t>TDE1b.Entregue aqui o LINK do vídeo de apresentação do projeto – ETAPA 2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -2346,11 +2385,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CRE12.Cumulative Reinforcement Exercise 12 - Sistemas Operacionais</t>
+          <t>TDE1c.Entregue aqui o PPT de apresentação do projeto – ETAPA 2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2361,55 +2400,10 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CRE13.Cumulative Reinforcement Exercise 13 - Comunicação de Dados</t>
+          <t>TDE1d.Apresentação do Projeto</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Fundamentos Sistemas Ciberfisicos</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>TDE1b.Entregue aqui o LINK do vídeo de apresentação do projeto – ETAPA 2</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Fundamentos Sistemas Ciberfisicos</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>TDE1c.Entregue aqui o PPT de apresentação do projeto – ETAPA 2</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Fundamentos Sistemas Ciberfisicos</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>TDE1d.Apresentação do Projeto</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
         <v>10</v>
       </c>
     </row>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -1815,7 +1815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1963,6 +1963,18 @@
       <c r="B12" t="inlineStr">
         <is>
           <t>TDE 6 - Funções</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Raciocinio Algoritmico</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Prova 3 - Recuperação RA2</t>
         </is>
       </c>
     </row>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -511,32 +511,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Atividade Extensionista</t>
-        </is>
+          <t>ATIVIDADE FORMATIVA 1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>9</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
+      <c r="D4" t="n">
+        <v>90</v>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Bom</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ATIVIDADE FORMATIVA 1</t>
+          <t>1ª AVALIAÇÃO SOMATIVA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -547,38 +553,38 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1ª AVALIAÇÃO SOMATIVA</t>
+          <t>Tarefa da aula 08 (21/05)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bom</t>
+          <t>Atencao</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tarefa da aula 08 (21/05)</t>
+          <t>2º AVALIAÇÃO SOMATIVA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -589,21 +595,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2º AVALIAÇÃO SOMATIVA</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>6</v>
+          <t>Atividade Extensionista</t>
+        </is>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
-      <c r="D8" t="n">
-        <v>60</v>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Atencao</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -1815,7 +1815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TDE - 23/02 - 27/02</t>
+          <t>RECUPERAÇÃO RA1</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aula 2 - TAREFA FORMATIVA - O valor da  filosofia</t>
+          <t>RECUPERAÇÃO RA2</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aula 3 - TAREFA FORMATIVA - KANT: resposta a pergunta o que é o esclarecimento</t>
+          <t>RECUPERAÇÃO RA3</t>
         </is>
       </c>
     </row>
@@ -1890,43 +1890,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aula 4 - TAREFA FORMATIVA - O equilibrista </t>
+          <t>TDE - 23/02 - 27/02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Raciocinio Algoritmico</t>
+          <t>Filosofia</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TDE 1 - Expressões aritméticas, lógicas e relacionais</t>
+          <t>Aula 2 - TAREFA FORMATIVA - O valor da  filosofia</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Raciocinio Algoritmico</t>
+          <t>Filosofia</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TDE 2 - Estruturas de Decisão</t>
+          <t>Aula 3 - TAREFA FORMATIVA - KANT: resposta a pergunta o que é o esclarecimento</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Raciocinio Algoritmico</t>
+          <t>Filosofia</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TDE 3 - Estruturas de Repetição</t>
+          <t xml:space="preserve">Aula 4 - TAREFA FORMATIVA - O equilibrista </t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TDE 4 - Vetores / Listas</t>
+          <t>TDE 1 - Expressões aritméticas, lógicas e relacionais</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TDE 5 - Matrizes</t>
+          <t>TDE 2 - Estruturas de Decisão</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TDE 6 - Funções</t>
+          <t>TDE 3 - Estruturas de Repetição</t>
         </is>
       </c>
     </row>
@@ -1973,6 +1973,42 @@
         </is>
       </c>
       <c r="B13" t="inlineStr">
+        <is>
+          <t>TDE 4 - Vetores / Listas</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Raciocinio Algoritmico</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TDE 5 - Matrizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Raciocinio Algoritmico</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TDE 6 - Funções</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Raciocinio Algoritmico</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Prova 3 - Recuperação RA2</t>
         </is>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -1239,7 +1239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -1636,17 +1636,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TDE1a.Entregue aqui o link do vídeo de especificação do projeto – ETAPA 1</t>
+          <t>B1.Bônus</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="C23" t="n">
         <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1657,22 +1657,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TDE1b.Entregue aqui o LINK do vídeo de apresentação do projeto – ETAPA 2</t>
-        </is>
+          <t>TDE1a.Entregue aqui o link do vídeo de especificação do projeto – ETAPA 1</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>10</v>
       </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atencao</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TDE1c.Entregue aqui o PPT de apresentação do projeto – ETAPA 2</t>
+          <t>TDE1b.Entregue aqui o LINK do vídeo de apresentação do projeto – ETAPA 2</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1687,7 +1693,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TDE1d.Apresentação do Projeto</t>
+          <t>TDE1c.Entregue aqui o PPT de apresentação do projeto – ETAPA 2</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1702,38 +1708,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RA1</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>4</v>
+          <t>TDE1d.Apresentação do Projeto</t>
+        </is>
       </c>
       <c r="C27" t="n">
         <v>10</v>
       </c>
-      <c r="D27" t="n">
-        <v>40</v>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atencao</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RA1r.Recuperação do RA1</t>
+          <t>RA1</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
         <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1744,61 +1744,82 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RA2</t>
+          <t>RA1r.Recuperação do RA1</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="C29" t="n">
         <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bom</t>
+          <t>Atencao</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RA3</t>
+          <t>RA2</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="C30" t="n">
         <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atencao</t>
+          <t>Bom</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>RA3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>MF.Média Final</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C31" t="n">
-        <v>10</v>
-      </c>
-      <c r="D31" t="n">
-        <v>38</v>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" t="n">
+        <v>40</v>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>Atencao</t>
         </is>
@@ -2119,19 +2140,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61.4</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="D4" t="n">
         <v>467</v>
       </c>
       <c r="E4" t="n">
-        <v>49.92</v>
+        <v>48.2</v>
       </c>
       <c r="F4" t="n">
-        <v>49.92</v>
+        <v>48.2</v>
       </c>
     </row>
   </sheetData>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -618,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -763,7 +763,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nota RA1</t>
+          <t>Nota RA1 e RA2</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -881,6 +881,69 @@
         <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Prova 2</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>69</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Nota RA2 e RA3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>52</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Nota Final</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" t="n">
+        <v>63</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>Atencao</t>
         </is>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -1774,12 +1774,18 @@
           <t>TDE1d.Apresentação do Projeto</t>
         </is>
       </c>
+      <c r="B27" t="n">
+        <v>10</v>
+      </c>
       <c r="C27" t="n">
         <v>10</v>
       </c>
+      <c r="D27" t="n">
+        <v>100</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Bom</t>
         </is>
       </c>
     </row>
@@ -2203,19 +2209,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64.09999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="D4" t="n">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="E4" t="n">
-        <v>48.2</v>
+        <v>51.82</v>
       </c>
       <c r="F4" t="n">
-        <v>48.2</v>
+        <v>51.82</v>
       </c>
     </row>
   </sheetData>
@@ -2229,7 +2235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2524,21 +2530,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Fundamentos Sistemas Ciberfisicos</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>TDE1d.Apresentação do Projeto</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -1859,13 +1859,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
         <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1880,13 +1880,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="C32" t="n">
         <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="C4" t="n">
         <v>143</v>
@@ -2218,10 +2218,10 @@
         <v>457</v>
       </c>
       <c r="E4" t="n">
-        <v>51.82</v>
+        <v>56.5</v>
       </c>
       <c r="F4" t="n">
-        <v>51.82</v>
+        <v>56.5</v>
       </c>
     </row>
   </sheetData>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -1724,17 +1724,17 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C24" t="n">
         <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atencao</t>
+          <t>Bom</t>
         </is>
       </c>
     </row>
@@ -1859,17 +1859,17 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C31" t="n">
         <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atencao</t>
+          <t>Bom</t>
         </is>
       </c>
     </row>
@@ -1880,17 +1880,17 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5.7</v>
+        <v>7.3</v>
       </c>
       <c r="C32" t="n">
         <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atencao</t>
+          <t>Bom</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80.8</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="C4" t="n">
         <v>143</v>
@@ -2218,10 +2218,10 @@
         <v>457</v>
       </c>
       <c r="E4" t="n">
-        <v>56.5</v>
+        <v>68.11</v>
       </c>
       <c r="F4" t="n">
-        <v>56.5</v>
+        <v>68.11</v>
       </c>
     </row>
   </sheetData>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2101,6 +2101,18 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>Prova 3 - Recuperação RA2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Raciocinio Algoritmico</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Prova 4 - Final (RA1 e RA2)</t>
         </is>
       </c>
     </row>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -7,9 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Nao_Contabilizadas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Pendentes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Aspectos Legais" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Experiencia Criativa" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Filosofia" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Raciocinio Algoritmico" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Fundamentos Sistemas Ciberfisic" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Nao_Contabilizadas" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Resumo" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Pendentes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,14 +429,205 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Atividade</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Obtido</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Maximo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Entrega</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Atividade Aula 03</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Envio TDE</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ATIVIDADE FORMATIVA 1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>90</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1ª AVALIAÇÃO SOMATIVA</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tarefa da aula 08 (21/05)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2º AVALIAÇÃO SOMATIVA</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>60</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Atividade Extensionista</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-12T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61646/assignments/326537</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -444,21 +640,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="97" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Disciplina</t>
+          <t>Atividade</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -468,107 +663,311 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Maximo Atual</t>
+          <t>Maximo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Pontos Pendentes</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Media Atual (%)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Projecao Final (%)</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aspectos Legais</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Erro 401: {"errors":[{"message":"Expired access token.","expired_at":"2026-07-18T00:00:00Z"}]}</t>
+          <t>TDE 1 - Trabalho Discente Efetivo</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Atencao</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Experiencia Criativa</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Erro 401: {"errors":[{"message":"Expired access token.","expired_at":"2026-07-18T00:00:00Z"}]}</t>
+          <t>Atividade1 - Esteganografia</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Atencao</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Filosofia</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Erro 401: {"errors":[{"message":"Expired access token.","expired_at":"2026-07-18T00:00:00Z"}]}</t>
+          <t>Atividade2 - Autenticação Firebase</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>80</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bom</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Raciocinio Algoritmico</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Erro 401: {"errors":[{"message":"Expired access token.","expired_at":"2026-07-18T00:00:00Z"}]}</t>
+          <t>Atividade3 - Controle de Acesso - Permissões Linux</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bom</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fundamentos Sistemas Ciberfisicos</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Erro 401: {"errors":[{"message":"Expired access token.","expired_at":"2026-07-18T00:00:00Z"}]}</t>
+          <t>Prova 1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>84</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Nota RA1 e RA2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>74</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Atividade4 - Análise de Desempenho Criptográfico</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atividade5 - Explorando o Ambiente Linux </t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Atividade6 - Estudo de Caso - Incidentes Cibernéticos</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Atividade7 - Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Atividade8 - Sistemas de Detecção de Intrusão</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Prova 2</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>69</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Nota RA2 e RA3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>52</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Nota Final</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" t="n">
+        <v>63</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Atencao</t>
         </is>
       </c>
     </row>
@@ -583,14 +982,1973 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Atividade</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Obtido</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Maximo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aula 4 - TAREFA SOMATIVA - O existencialismo é um humanismo </t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ATIVIDADE AVALIATIVA SOMATIVA - PROVA RA1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aula 6 - TAREFA SOMATIVA - A sociedade do cansaço </t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>90</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aula 5 - TAREFA - Arendt e a condição humana</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TDE - parte 1 - TAREFA SOMATIVA - A inteligência artificial vai nos superar? </t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TDE - parte 2 - TAREFA SOMATIVA - Educação: a mudança é a única constante</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TDE - parte final - ENTREGA do LINK</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Atividade</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Obtido</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Maximo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Entrega</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PjBL 1 - Folha de Pagamento</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>76</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Prova 1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-05-05T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61650/assignments/322534</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PjBL 2 - Batalha Naval</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Teste 2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Teste 2 - Correção</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="76" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Atividade</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Obtido</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Maximo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Entrega</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>S1.Avaliação Somativa 1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>S2.Avaliação Somativa 2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>44</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>S3.Avaliação Somativa 3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>71</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Conversão de Bases - Exercícios Adionais</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>48</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-25T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/318593</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Limites números binários - Exercícios Adicionais</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>49</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-25T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/318598</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Números Negativos - Exercícios Adicionais</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-25T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/318599</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Operações em Outras Bases - Exercícios Adicionais</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>49</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-25T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/318600</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Bitwise - Exercícios Adicionais</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>48</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-23T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/318601</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CRE1.Cumulative Reinforcement Exercise 1</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-30T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/313565</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CRE2.Cumulative Reinforcement Exercise 2</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-07T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/316281</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CRE3.Cumulative Reinforcement Exercise 3</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-07T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/316282</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CRE4.Cumulative Reinforcement Exercise 4</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CRE5.Cumulative Reinforcement Exercise 5</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CRE6.Cumulative Reinforcement Exercise 6</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CRE7.Cumulative Reinforcement Exercise 7 - Máquinas de Turing</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CRE8.Cumulative Reinforcement Exercise 8</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>27</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-25T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/318561</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CRE9.Cumulative Reinforcement Exercise 9</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>34</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/325300</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CRE10.Cumulative Reinforcement Exercise 10</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/325301</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CRE11.Cumulative Reinforcement Exercise 11</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>15</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/325302</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CRE12.Cumulative Reinforcement Exercise 12 - Sistemas Operacionais</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>33</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-20T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/328207</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CRE13.Cumulative Reinforcement Exercise 13 - Comunicação de Dados</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>33</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-20T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/328210</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>B1.Bônus</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TDE1a.Entregue aqui o link do vídeo de especificação do projeto – ETAPA 1</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TDE1b.Entregue aqui o LINK do vídeo de apresentação do projeto – ETAPA 2</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-26T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/331262</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TDE1c.Entregue aqui o PPT de apresentação do projeto – ETAPA 2</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-26T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/331264</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TDE1d.Apresentação do Projeto</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RA1</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>40</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RA1r.Recuperação do RA1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" t="n">
+        <v>44</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Atencao</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RA2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" t="n">
+        <v>71</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RA3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MF.Média Final</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C32" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" t="n">
+        <v>73</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="81" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Disciplina</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Atividade</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Experiencia Criativa</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TDE - Semana de Integração</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Filosofia</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO RA1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Filosofia</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO RA2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Filosofia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO RA3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Filosofia</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TDE - 23/02 - 27/02</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Filosofia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Aula 2 - TAREFA FORMATIVA - O valor da  filosofia</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Filosofia</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aula 3 - TAREFA FORMATIVA - KANT: resposta a pergunta o que é o esclarecimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Filosofia</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aula 4 - TAREFA FORMATIVA - O equilibrista </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Raciocinio Algoritmico</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TDE 1 - Expressões aritméticas, lógicas e relacionais</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Raciocinio Algoritmico</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TDE 2 - Estruturas de Decisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Raciocinio Algoritmico</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TDE 3 - Estruturas de Repetição</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Raciocinio Algoritmico</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TDE 4 - Vetores / Listas</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Raciocinio Algoritmico</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TDE 5 - Matrizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Raciocinio Algoritmico</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TDE 6 - Funções</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Raciocinio Algoritmico</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Prova 3 - Recuperação RA2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Raciocinio Algoritmico</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Prova 4 - Final (RA1 e RA2)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Disciplina</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Obtido</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Maximo Atual</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Pontos Pendentes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Media Atual (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Projecao Final (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aspectos Legais</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.67</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Raciocinio Algoritmico</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="C3" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="F3" t="n">
+        <v>55.72</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="C4" t="n">
+        <v>143</v>
+      </c>
+      <c r="D4" t="n">
+        <v>457</v>
+      </c>
+      <c r="E4" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="F4" t="n">
+        <v>68.11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="75" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Disciplina</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Atividade</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Entrega</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Maximo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aspectos Legais</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Atividade Extensionista</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-12T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61646/assignments/326537</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Raciocinio Algoritmico</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Prova 1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-05T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61650/assignments/322534</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Conversão de Bases - Exercícios Adionais</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-04-25T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/318593</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Limites números binários - Exercícios Adicionais</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-04-25T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>49</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/318598</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Números Negativos - Exercícios Adicionais</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-04-25T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/318599</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Operações em Outras Bases - Exercícios Adicionais</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04-25T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>49</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/318600</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bitwise - Exercícios Adicionais</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-04-23T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>48</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/318601</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CRE1.Cumulative Reinforcement Exercise 1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-03-30T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/313565</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CRE2.Cumulative Reinforcement Exercise 2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-04-07T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/316281</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CRE3.Cumulative Reinforcement Exercise 3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-04-07T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/316282</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CRE8.Cumulative Reinforcement Exercise 8</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-04-25T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>27</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/318561</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CRE9.Cumulative Reinforcement Exercise 9</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>34</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/325300</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CRE10.Cumulative Reinforcement Exercise 10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/325301</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CRE11.Cumulative Reinforcement Exercise 11</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>15</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/325302</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CRE12.Cumulative Reinforcement Exercise 12 - Sistemas Operacionais</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-06-20T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>33</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/328207</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CRE13.Cumulative Reinforcement Exercise 13 - Comunicação de Dados</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06-20T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>33</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/328210</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TDE1b.Entregue aqui o LINK do vídeo de apresentação do projeto – ETAPA 2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06-26T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/331262</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas Ciberfisicos</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TDE1c.Entregue aqui o PPT de apresentação do projeto – ETAPA 2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06-26T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/61660/assignments/331264</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -2343,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2411,44 +2411,88 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Raciocinio Algoritmico</t>
+          <t>Experiencia Criativa</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.11</v>
+        <v>71.2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.5</v>
+        <v>140</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>55.72</v>
+        <v>50.86</v>
       </c>
       <c r="F3" t="n">
-        <v>55.72</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Filosofia</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>46</v>
+      </c>
+      <c r="C4" t="n">
+        <v>70</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>65.70999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>65.70999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Raciocinio Algoritmico</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="C5" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="F5" t="n">
+        <v>55.72</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Fundamentos Sistemas Ciberfisicos</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B6" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C6" t="n">
         <v>143</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D6" t="n">
         <v>457</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E6" t="n">
         <v>68.11</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F6" t="n">
         <v>68.11</v>
       </c>
     </row>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -426,10 +426,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -522,6 +522,31 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>https://pucpr.instructure.com/courses/71920/assignments/350693</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Atividade2 - Configuração de Rede (Packet Tracer)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-21T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/352471</t>
         </is>
       </c>
     </row>
@@ -896,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -982,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1072,20 +1097,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Criptografia Aplicada</t>
+          <t>Conectividade e Sistemas Ciberfísicos</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SOMATIVA 1A: Modo de Blocos do Algoritmo AES (RA1)</t>
+          <t>Atividade2 - Configuração de Rede (Packet Tracer)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-08-21T02:59:59Z</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338790</t>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/352471</t>
         </is>
       </c>
     </row>
@@ -1097,15 +1127,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SOMATIVA 1B: Negociação ECDH (RA1)</t>
+          <t>SOMATIVA 1A: Modo de Blocos do Algoritmo AES (RA1)</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338791</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338790</t>
         </is>
       </c>
     </row>
@@ -1117,15 +1147,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SOMATIVA 1C: Modelo criptográfico híbrido do PGP (RA1)</t>
+          <t>SOMATIVA 1B: Negociação ECDH (RA1)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338792</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338791</t>
         </is>
       </c>
     </row>
@@ -1137,15 +1167,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SOMATIVA 2A: Autenticação com SALT (RA2)</t>
+          <t>SOMATIVA 1C: Modelo criptográfico híbrido do PGP (RA1)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338793</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338792</t>
         </is>
       </c>
     </row>
@@ -1157,15 +1187,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SOMATIVA 2B: Autenticação Mútua e Challenge -SCRAM (RA 2)</t>
+          <t>SOMATIVA 2A: Autenticação com SALT (RA2)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338794</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338793</t>
         </is>
       </c>
     </row>
@@ -1177,15 +1207,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SOMATIVA 4: Aplicações com API TLS (RA2)</t>
+          <t>SOMATIVA 2B: Autenticação Mútua e Challenge -SCRAM (RA 2)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338796</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338794</t>
         </is>
       </c>
     </row>
@@ -1197,15 +1227,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TDE 1: Identificação por assinatura digital (RA3)</t>
+          <t>SOMATIVA 4: Aplicações com API TLS (RA2)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338797</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338796</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1247,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TDE 2: Análise de uma captura HTTPS (RA3)</t>
+          <t>TDE 1: Identificação por assinatura digital (RA3)</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1225,7 +1255,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338798</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338797</t>
         </is>
       </c>
     </row>
@@ -1237,13 +1267,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>TDE 2: Análise de uma captura HTTPS (RA3)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338798</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Criptografia Aplicada</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t xml:space="preserve">SOMATIVA 3: Criação e uso de Certificados Digitais (RA 3) </t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D13" t="n">
         <v>4</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://pucpr.instructure.com/courses/71912/assignments/338795</t>
         </is>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Conectividade e Sistemas Ciberf" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Criptografia Aplicada" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Nao_Contabilizadas" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Resumo" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Pendentes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Arquitetura de Banco de Dados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Conectividade e Sistemas Ciberf" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Criptografia Aplicada" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Nao_Contabilizadas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Resumo" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Pendentes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Atividade</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Entrega</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Obtido</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Maximo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TDE 1 - Entrega</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-08-22T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71926/assignments/351273</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PjBL Parte 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08-22T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71926/assignments/353921</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -550,12 +661,37 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Atividade Prática 3 / Relatório Packet Tracer 2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-31T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/353858</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -795,7 +931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -815,7 +951,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -899,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -921,7 +1057,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1001,13 +1137,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1047,17 +1183,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Conectividade e Sistemas Ciberfísicos</t>
+          <t>Arquitetura de Banco de Dados</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TDE 1 - Trabalho Discente Efetivo</t>
+          <t>TDE 1 - Entrega</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-14T02:59:59Z</t>
+          <t>2026-08-22T02:59:59Z</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1065,32 +1201,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71920/assignments/342276</t>
+          <t>https://pucpr.instructure.com/courses/71926/assignments/351273</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Conectividade e Sistemas Ciberfísicos</t>
+          <t>Arquitetura de Banco de Dados</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Atividade1 -  Wireshark</t>
+          <t>PjBL Parte 1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-14T02:59:59Z</t>
+          <t>2026-08-22T02:59:59Z</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71920/assignments/350693</t>
+          <t>https://pucpr.instructure.com/courses/71926/assignments/353921</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1238,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Atividade2 - Configuração de Rede (Packet Tracer)</t>
+          <t>TDE 1 - Trabalho Discente Efetivo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-21T02:59:59Z</t>
+          <t>2026-09-14T02:59:59Z</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1115,67 +1251,82 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71920/assignments/352471</t>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/342276</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Criptografia Aplicada</t>
+          <t>Conectividade e Sistemas Ciberfísicos</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SOMATIVA 1A: Modo de Blocos do Algoritmo AES (RA1)</t>
+          <t>Atividade1 -  Wireshark</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-08-14T02:59:59Z</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338790</t>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/350693</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Criptografia Aplicada</t>
+          <t>Conectividade e Sistemas Ciberfísicos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SOMATIVA 1B: Negociação ECDH (RA1)</t>
+          <t>Atividade2 - Configuração de Rede (Packet Tracer)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-08-21T02:59:59Z</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338791</t>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/352471</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Criptografia Aplicada</t>
+          <t>Conectividade e Sistemas Ciberfísicos</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SOMATIVA 1C: Modelo criptográfico híbrido do PGP (RA1)</t>
+          <t>Atividade Prática 3 / Relatório Packet Tracer 2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-08-31T02:59:59Z</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338792</t>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/353858</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1338,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SOMATIVA 2A: Autenticação com SALT (RA2)</t>
+          <t>SOMATIVA 1A: Modo de Blocos do Algoritmo AES (RA1)</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1195,7 +1346,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338793</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338790</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1358,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SOMATIVA 2B: Autenticação Mútua e Challenge -SCRAM (RA 2)</t>
+          <t>SOMATIVA 1B: Negociação ECDH (RA1)</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1215,7 +1366,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338794</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338791</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1378,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SOMATIVA 4: Aplicações com API TLS (RA2)</t>
+          <t>SOMATIVA 1C: Modelo criptográfico híbrido do PGP (RA1)</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1235,7 +1386,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338796</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338792</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1398,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TDE 1: Identificação por assinatura digital (RA3)</t>
+          <t>SOMATIVA 2A: Autenticação com SALT (RA2)</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1255,7 +1406,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338797</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338793</t>
         </is>
       </c>
     </row>
@@ -1267,15 +1418,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TDE 2: Análise de uma captura HTTPS (RA3)</t>
+          <t>SOMATIVA 2B: Autenticação Mútua e Challenge -SCRAM (RA 2)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338798</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338794</t>
         </is>
       </c>
     </row>
@@ -1287,13 +1438,73 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>SOMATIVA 4: Aplicações com API TLS (RA2)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338796</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Criptografia Aplicada</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TDE 1: Identificação por assinatura digital (RA3)</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338797</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Criptografia Aplicada</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TDE 2: Análise de uma captura HTTPS (RA3)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338798</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Criptografia Aplicada</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t xml:space="preserve">SOMATIVA 3: Criação e uso de Certificados Digitais (RA 3) </t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D16" t="n">
         <v>4</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://pucpr.instructure.com/courses/71912/assignments/338795</t>
         </is>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -937,14 +937,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Disciplina</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Atividade</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Arquitetura de Banco de Dados</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PjBL - codigo sql</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -701,7 +701,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="61" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -750,6 +750,11 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>SOMATIVA 1A: Modo de Blocos do Algoritmo AES (RA1)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-09T02:59:59Z</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1363,6 +1368,11 @@
           <t>SOMATIVA 1A: Modo de Blocos do Algoritmo AES (RA1)</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-09-09T02:59:59Z</t>
+        </is>
+      </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -537,10 +537,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -639,7 +639,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Atividade2 - Configuração de Rede (Packet Tracer)</t>
+          <t>Atividade Prática2 - Configuração de Rede - Hub e Switch (Packet Tracer)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Atividade Prática 3 / Relatório Packet Tracer 2</t>
+          <t>Atividade Prática3 - Configuração de Rede - Roteamento (Packet Tracer)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -683,6 +683,31 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>https://pucpr.instructure.com/courses/71920/assignments/353858</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Atividade Prática4 - Configuração de Rede - Topologia da Rede (Packet Tracer)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-07T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/356766</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1170,11 +1195,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="61" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
@@ -1315,7 +1340,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Atividade2 - Configuração de Rede (Packet Tracer)</t>
+          <t>Atividade Prática2 - Configuração de Rede - Hub e Switch (Packet Tracer)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1340,7 +1365,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Atividade Prática 3 / Relatório Packet Tracer 2</t>
+          <t>Atividade Prática3 - Configuração de Rede - Roteamento (Packet Tracer)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1360,25 +1385,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Criptografia Aplicada</t>
+          <t>Conectividade e Sistemas Ciberfísicos</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SOMATIVA 1A: Modo de Blocos do Algoritmo AES (RA1)</t>
+          <t>Atividade Prática4 - Configuração de Rede - Topologia da Rede (Packet Tracer)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-09T02:59:59Z</t>
+          <t>2026-09-07T02:59:59Z</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338790</t>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/356766</t>
         </is>
       </c>
     </row>
@@ -1390,15 +1415,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SOMATIVA 1B: Negociação ECDH (RA1)</t>
+          <t>SOMATIVA 1A: Modo de Blocos do Algoritmo AES (RA1)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-09-09T02:59:59Z</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338791</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338790</t>
         </is>
       </c>
     </row>
@@ -1410,15 +1440,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SOMATIVA 1C: Modelo criptográfico híbrido do PGP (RA1)</t>
+          <t>SOMATIVA 1B: Negociação ECDH (RA1)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338792</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338791</t>
         </is>
       </c>
     </row>
@@ -1430,15 +1460,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SOMATIVA 2A: Autenticação com SALT (RA2)</t>
+          <t>SOMATIVA 1C: Modelo criptográfico híbrido do PGP (RA1)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338793</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338792</t>
         </is>
       </c>
     </row>
@@ -1450,15 +1480,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SOMATIVA 2B: Autenticação Mútua e Challenge -SCRAM (RA 2)</t>
+          <t>SOMATIVA 2A: Autenticação com SALT (RA2)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338794</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338793</t>
         </is>
       </c>
     </row>
@@ -1470,15 +1500,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SOMATIVA 4: Aplicações com API TLS (RA2)</t>
+          <t>SOMATIVA 2B: Autenticação Mútua e Challenge -SCRAM (RA 2)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338796</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338794</t>
         </is>
       </c>
     </row>
@@ -1490,15 +1520,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TDE 1: Identificação por assinatura digital (RA3)</t>
+          <t>SOMATIVA 4: Aplicações com API TLS (RA2)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338797</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338796</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1540,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TDE 2: Análise de uma captura HTTPS (RA3)</t>
+          <t>TDE 1: Identificação por assinatura digital (RA3)</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1518,7 +1548,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338798</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338797</t>
         </is>
       </c>
     </row>
@@ -1530,13 +1560,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>TDE 2: Análise de uma captura HTTPS (RA3)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338798</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Criptografia Aplicada</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t xml:space="preserve">SOMATIVA 3: Criação e uso de Certificados Digitais (RA 3) </t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D17" t="n">
         <v>4</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://pucpr.instructure.com/courses/71912/assignments/338795</t>
         </is>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -708,6 +708,31 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>https://pucpr.instructure.com/courses/71920/assignments/356766</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Atividade Prática 5 - Relatório Socket API</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-18T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/357886</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1134,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1195,7 +1220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1410,25 +1435,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Criptografia Aplicada</t>
+          <t>Conectividade e Sistemas Ciberfísicos</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SOMATIVA 1A: Modo de Blocos do Algoritmo AES (RA1)</t>
+          <t>Atividade Prática 5 - Relatório Socket API</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-09T02:59:59Z</t>
+          <t>2026-09-18T02:59:59Z</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338790</t>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/357886</t>
         </is>
       </c>
     </row>
@@ -1440,15 +1465,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SOMATIVA 1B: Negociação ECDH (RA1)</t>
+          <t>SOMATIVA 1A: Modo de Blocos do Algoritmo AES (RA1)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-09-09T02:59:59Z</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338791</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338790</t>
         </is>
       </c>
     </row>
@@ -1460,15 +1490,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SOMATIVA 1C: Modelo criptográfico híbrido do PGP (RA1)</t>
+          <t>SOMATIVA 1B: Negociação ECDH (RA1)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338792</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338791</t>
         </is>
       </c>
     </row>
@@ -1480,15 +1510,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SOMATIVA 2A: Autenticação com SALT (RA2)</t>
+          <t>SOMATIVA 1C: Modelo criptográfico híbrido do PGP (RA1)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338793</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338792</t>
         </is>
       </c>
     </row>
@@ -1500,15 +1530,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SOMATIVA 2B: Autenticação Mútua e Challenge -SCRAM (RA 2)</t>
+          <t>SOMATIVA 2A: Autenticação com SALT (RA2)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338794</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338793</t>
         </is>
       </c>
     </row>
@@ -1520,15 +1550,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SOMATIVA 4: Aplicações com API TLS (RA2)</t>
+          <t>SOMATIVA 2B: Autenticação Mútua e Challenge -SCRAM (RA 2)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338796</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338794</t>
         </is>
       </c>
     </row>
@@ -1540,15 +1570,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TDE 1: Identificação por assinatura digital (RA3)</t>
+          <t>SOMATIVA 4: Aplicações com API TLS (RA2)</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338797</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338796</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1590,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TDE 2: Análise de uma captura HTTPS (RA3)</t>
+          <t>TDE 1: Identificação por assinatura digital (RA3)</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1568,7 +1598,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338798</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338797</t>
         </is>
       </c>
     </row>
@@ -1580,13 +1610,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>TDE 2: Análise de uma captura HTTPS (RA3)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338798</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Criptografia Aplicada</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t xml:space="preserve">SOMATIVA 3: Criação e uso de Certificados Digitais (RA 3) </t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D18" t="n">
         <v>4</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://pucpr.instructure.com/courses/71912/assignments/338795</t>
         </is>
